--- a/menus/Menu_Russian_Final.xlsx
+++ b/menus/Menu_Russian_Final.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jovnerinos\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\justadd\menus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F64E30C-BEC4-4D1E-B4F1-84C55F4FD1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4EFC90-8A18-4F59-A453-9778F1272959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -551,11 +551,21 @@
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -564,20 +574,10 @@
     <xf numFmtId="44" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -959,23 +959,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="21"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="18"/>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
@@ -987,23 +987,23 @@
       <c r="K2" s="17"/>
     </row>
     <row r="3" spans="1:15" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="20"/>
+      <c r="B3" s="24"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
       <c r="I3" s="13"/>
-      <c r="J3" s="19" t="s">
+      <c r="J3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="23"/>
+      <c r="K3" s="26"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D4" s="4"/>
@@ -1012,19 +1012,19 @@
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="D5" s="18" t="s">
+      <c r="B5" s="18"/>
+      <c r="D5" s="16" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="17"/>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="J5" s="18" t="s">
+      <c r="H5" s="16"/>
+      <c r="J5" s="16" t="s">
         <v>6</v>
       </c>
       <c r="K5" s="17"/>
@@ -1110,7 +1110,7 @@
       <c r="B9" s="15">
         <v>12</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="16" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="17"/>
@@ -1137,17 +1137,17 @@
       <c r="H10" s="11">
         <v>10</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="16" t="s">
         <v>23</v>
       </c>
       <c r="K10" s="17"/>
       <c r="O10" s="9"/>
     </row>
     <row r="11" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="21"/>
+      <c r="B11" s="18"/>
       <c r="D11" s="10" t="s">
         <v>25</v>
       </c>
@@ -1240,7 +1240,7 @@
       <c r="B15" s="15">
         <v>10</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="16" t="s">
         <v>34</v>
       </c>
       <c r="E15" s="17"/>
@@ -1331,10 +1331,10 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="21"/>
+      <c r="B19" s="18"/>
       <c r="D19" s="10" t="s">
         <v>37</v>
       </c>
@@ -1497,7 +1497,7 @@
       <c r="H26" s="11">
         <v>12</v>
       </c>
-      <c r="J26" s="18" t="s">
+      <c r="J26" s="16" t="s">
         <v>69</v>
       </c>
       <c r="K26" s="17"/>
@@ -1574,10 +1574,10 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="21"/>
+      <c r="B30" s="18"/>
       <c r="D30" s="10" t="s">
         <v>81</v>
       </c>
@@ -1652,7 +1652,7 @@
       <c r="B33" s="15">
         <v>10</v>
       </c>
-      <c r="J33" s="18" t="s">
+      <c r="J33" s="16" t="s">
         <v>55</v>
       </c>
       <c r="K33" s="17"/>
@@ -1664,9 +1664,9 @@
       <c r="B34" s="15">
         <v>10</v>
       </c>
-      <c r="D34" s="16"/>
+      <c r="D34" s="22"/>
       <c r="E34" s="17"/>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="25" t="s">
         <v>108</v>
       </c>
       <c r="G34" s="17"/>
@@ -1705,7 +1705,7 @@
       <c r="F36" s="17"/>
       <c r="G36" s="17"/>
       <c r="H36" s="17"/>
-      <c r="J36" s="18" t="s">
+      <c r="J36" s="16" t="s">
         <v>95</v>
       </c>
       <c r="K36" s="17"/>
@@ -1725,10 +1725,10 @@
       </c>
     </row>
     <row r="38" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B38" s="21"/>
+      <c r="B38" s="18"/>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="17"/>
@@ -1816,11 +1816,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
     <mergeCell ref="D34:E42"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="A3:B3"/>
@@ -1837,6 +1832,11 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="A30:B30"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
   <pageMargins left="1.1023622047244095" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="61" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -1854,7 +1854,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="22" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="17"/>
